--- a/results/For_Others/Job_Search_Tracking.xlsx
+++ b/results/For_Others/Job_Search_Tracking.xlsx
@@ -103,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -118,6 +118,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -610,17 +613,37 @@
           <t>Aaron Kimson</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse/Lever/Ashby/LinkedIn | L/S HF Analyst, HF PM, Dir ER, Inv Analyst | NY, SF, Chicago, Miami, Boston</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Aaron/Week_of_2026-02-09/</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
